--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/VIRGINIA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/VIRGINIA_2016.xlsx
@@ -589,7 +589,7 @@
         <v>5</v>
       </c>
       <c r="D13">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="14">
@@ -697,7 +697,7 @@
         <v>5</v>
       </c>
       <c r="D19">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         <v>5</v>
       </c>
       <c r="D22">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="23">
@@ -877,7 +877,7 @@
         <v>5</v>
       </c>
       <c r="D29">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="30">
@@ -1561,7 +1561,7 @@
         <v>5</v>
       </c>
       <c r="D67">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="68">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C93">
@@ -3667,7 +3667,7 @@
         <v>5</v>
       </c>
       <c r="D184">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="185">
@@ -3739,7 +3739,7 @@
         <v>5</v>
       </c>
       <c r="D188">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="189">
@@ -4081,7 +4081,7 @@
         <v>5</v>
       </c>
       <c r="D207">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="208">
@@ -4135,7 +4135,7 @@
         <v>5</v>
       </c>
       <c r="D210">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="211">
@@ -4153,7 +4153,7 @@
         <v>5</v>
       </c>
       <c r="D211">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="212">
@@ -4189,7 +4189,7 @@
         <v>5</v>
       </c>
       <c r="D213">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="214">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C214">
@@ -4873,7 +4873,7 @@
         <v>5</v>
       </c>
       <c r="D251">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="252">
@@ -5377,7 +5377,7 @@
         <v>5</v>
       </c>
       <c r="D279">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="280">
@@ -5503,7 +5503,7 @@
         <v>5</v>
       </c>
       <c r="D286">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="287">
@@ -6187,7 +6187,7 @@
         <v>5</v>
       </c>
       <c r="D324">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="325">
@@ -6439,7 +6439,7 @@
         <v>5</v>
       </c>
       <c r="D338">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="339">
@@ -7015,7 +7015,7 @@
         <v>5</v>
       </c>
       <c r="D370">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="371">
@@ -7069,7 +7069,7 @@
         <v>5</v>
       </c>
       <c r="D373">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="374">
@@ -7213,7 +7213,7 @@
         <v>5</v>
       </c>
       <c r="D381">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="382">
@@ -8563,7 +8563,7 @@
         <v>5</v>
       </c>
       <c r="D456">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="457">
@@ -8779,7 +8779,7 @@
         <v>5</v>
       </c>
       <c r="D468">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="469">
@@ -8923,7 +8923,7 @@
         <v>5</v>
       </c>
       <c r="D476">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="477">
@@ -9373,7 +9373,7 @@
         <v>5</v>
       </c>
       <c r="D501">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="502">
@@ -9949,7 +9949,7 @@
         <v>5</v>
       </c>
       <c r="D533">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="534">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C548">
@@ -10255,7 +10255,7 @@
         <v>5</v>
       </c>
       <c r="D550">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="551">
@@ -10507,7 +10507,7 @@
         <v>5</v>
       </c>
       <c r="D564">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="565">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C569">
@@ -10939,7 +10939,7 @@
         <v>5</v>
       </c>
       <c r="D588">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="589">
@@ -10975,7 +10975,7 @@
         <v>5</v>
       </c>
       <c r="D590">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="591">
@@ -11245,7 +11245,7 @@
         <v>5</v>
       </c>
       <c r="D605">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="606">
@@ -11551,7 +11551,7 @@
         <v>5</v>
       </c>
       <c r="D622">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="623">
@@ -11911,7 +11911,7 @@
         <v>5</v>
       </c>
       <c r="D642">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="643">
@@ -12307,7 +12307,7 @@
         <v>5</v>
       </c>
       <c r="D664">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="665">
@@ -13351,7 +13351,7 @@
         <v>5</v>
       </c>
       <c r="D722">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="723">
@@ -13621,7 +13621,7 @@
         <v>5</v>
       </c>
       <c r="D737">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="738">
@@ -14251,7 +14251,7 @@
         <v>5</v>
       </c>
       <c r="D772">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="773">
@@ -14719,7 +14719,7 @@
         <v>5</v>
       </c>
       <c r="D798">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="799">
@@ -14845,7 +14845,7 @@
         <v>5</v>
       </c>
       <c r="D805">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="806">
@@ -15205,7 +15205,7 @@
         <v>5</v>
       </c>
       <c r="D825">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="826">
@@ -16519,7 +16519,7 @@
         <v>5</v>
       </c>
       <c r="D898">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="899">
@@ -16825,7 +16825,7 @@
         <v>5</v>
       </c>
       <c r="D915">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="916">
@@ -16843,7 +16843,7 @@
         <v>5</v>
       </c>
       <c r="D916">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="917">
@@ -18085,7 +18085,7 @@
         <v>5</v>
       </c>
       <c r="D985">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="986">
@@ -18139,7 +18139,7 @@
         <v>5</v>
       </c>
       <c r="D988">
-        <v>0.0009697439875872769</v>
+        <v>0.0009697439875872768</v>
       </c>
     </row>
     <row r="989">
